--- a/outputs/01a0ce44-update-20260929/Station_Code_Guide.xlsx
+++ b/outputs/01a0ce44-update-20260929/Station_Code_Guide.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\theer\Documents\GitHub\compact_3_station_auto_inkjet\outputs\01a0ce44-update-20260929\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC86FC7B-5309-4CF8-8CFF-286EF409C9D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41D6393-4409-4D97-BC06-C08BA2CD9948}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9600" yWindow="5500" windowWidth="28800" windowHeight="15380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="อ่านโค้ด Flow Station barcode" sheetId="1" r:id="rId1"/>
@@ -35,9 +35,6 @@
     <t>อ่านโค้ด Flow Station barcode</t>
   </si>
   <si>
-    <t>อ้างอิง fix-after-it-test @ 896b34b | 29/09/2569</t>
-  </si>
-  <si>
     <t>Mode 0: สแกน Lot → ตรวจและแก้ Qty → สร้าง Job กับข้อมูลประกอบ → Station 1/3 อ่านจาก Backend</t>
   </si>
   <si>
@@ -61,11 +58,6 @@
 AppSettingsFile.Resolve(): หาไฟล์ใน ProgramData</t>
   </si>
   <si>
-    <t>Program.cs:14
-MainShellForm.cs:146
-AppSettingsFile.cs:39</t>
-  </si>
-  <si>
     <t>เข้า Scan Barcode
 ค่าตั้งแยกจากโฟลเดอร์ Build</t>
   </si>
@@ -75,10 +67,6 @@
   <si>
     <t>TxtBarcode_KeyDown(): รับ Enter
 LoadLot(false): ค้น Lot พร้อมแจ้งเหตุถ้าไม่พบ</t>
-  </si>
-  <si>
-    <t>ScanBarcodeUserControl.cs:98
-ScanBarcodeUserControl.cs:113</t>
   </si>
   <si>
     <t>ยังไม่สร้าง Job
@@ -93,10 +81,6 @@
 LoadLot(true): ค้นเงียบ ไม่เปิดกล่องเตือน</t>
   </si>
   <si>
-    <t>ScanBarcodeUserControl.cs:119
-ScanBarcodeUserControl.cs:113</t>
-  </si>
-  <si>
     <t>เปลี่ยน Barcode ต้องไม่ใช้ข้อมูล Lot เก่า</t>
   </si>
   <si>
@@ -108,10 +92,6 @@
 GetCustomer(): อ่านชื่อลูกค้า</t>
   </si>
   <si>
-    <t>SqliteDataService.cs:122
-SqliteDataService.cs:228</t>
-  </si>
-  <si>
     <t>ใช้ print_data / plan_routing / inkjet_data
 ช่องต้นทางว่าง แสดงว่าง</t>
   </si>
@@ -122,11 +102,6 @@
     <t>BtnEditQty_Click(): รับจำนวนเต็มมากกว่า 0
 ValidateForm(): ตรวจ Barcode ที่โหลดและ Qty
 BtnConfirm_Click(): ปิดปุ่มระหว่างสร้างงาน</t>
-  </si>
-  <si>
-    <t>ScanBarcodeUserControl.cs:188
-ScanBarcodeUserControl.cs:219
-ScanBarcodeUserControl.cs:202</t>
   </si>
   <si>
     <t>Qty เปลี่ยนเฉพาะ Job ที่กำลังสร้าง
@@ -142,10 +117,6 @@
 ConfirmClampDatabase(): ถามเมื่อไฟล์แคลมป์ไม่พร้อม</t>
   </si>
   <si>
-    <t>ScanBarcodeUserControl.cs:251
-ScanBarcodeUserControl.cs:360</t>
-  </si>
-  <si>
     <t>SQLite / Backend ไม่พร้อม: หยุด
 แคลมป์ไม่พร้อม: ผู้ใช้เลือกทำต่อได้</t>
   </si>
@@ -158,10 +129,6 @@
 GetPlanRouting(): อ่านวิธีพิมพ์และ Process seq</t>
   </si>
   <si>
-    <t>SqliteDataService.cs:26
-SqliteDataService.cs:168</t>
-  </si>
-  <si>
     <t>ไม่มี Pattern: หยุดก่อนสร้าง Job
 ไม่ส่งคำสั่งอุปกรณ์ในขั้นนี้</t>
   </si>
@@ -174,11 +141,6 @@
 Pattern ไม่ผ่าน: DeleteJobAsync() ขอถอน Job</t>
   </si>
   <si>
-    <t>ScanBarcodeUserControl.cs:251
-ApiClient.cs:81
-ApiClient.cs:98</t>
-  </si>
-  <si>
     <t>งานเริ่มเป็น Waiting
 คำขอแต่ละส่วนบันทึกแยกกัน</t>
   </si>
@@ -191,10 +153,6 @@
 ล้มเหลว: เตือน แล้วทำขั้นถัดไป</t>
   </si>
   <si>
-    <t>ApiClient.cs:172
-ApiClient.cs:255</t>
-  </si>
-  <si>
     <t>อาจมี Job แต่ข้อมูลประกอบไม่ครบ
 อย่าใช้กล่องสำเร็จยืนยันทุกตาราง</t>
   </si>
@@ -207,10 +165,6 @@
 CreateIaiAsync(): เก็บค่า IAI ของ Job</t>
   </si>
   <si>
-    <t>ScanBarcodeUserControl.cs:386
-ClampService.cs:195</t>
-  </si>
-  <si>
     <t>เป็นการเก็บค่า ไม่ได้สั่งแคลมป์วิ่ง
 ไม่มีชื่อโปรแกรมทั้งสองฝั่งให้ข้าม</t>
   </si>
@@ -223,10 +177,6 @@
 Focus(): กลับช่องรับ Barcode</t>
   </si>
   <si>
-    <t>ScanBarcodeUserControl.cs:437
-ScanBarcodeUserControl.cs:445</t>
-  </si>
-  <si>
     <t>อยู่หน้าเดิม รอสแกนใหม่</t>
   </si>
   <si>
@@ -238,11 +188,6 @@
 JobProcessService.Current(): แยก Online/Offline</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:661
-OrderListUserControl.cs:896
-JobProcessService.cs:32</t>
-  </si>
-  <si>
     <t>แต่ละ PC อ่าน Backend ร่วมกัน
 ไม่มีการเปิดหน้าต่างข้ามเครื่อง</t>
   </si>
@@ -273,10 +218,6 @@
 RefreshDataAsync(): อ่าน Job, คิว และคำขอ ST3</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:205
-OrderListUserControl.cs:661</t>
-  </si>
-  <si>
     <t>เข้า Order List
 ไม่ผูกตารางใหม่ระหว่างส่งข้อมูล</t>
   </si>
@@ -287,11 +228,6 @@
     <t>ApplyProcessTabs(): อ่านตัวเลือกแสดงแท็บ
 JobProcessService.Current(): ดู Process seq
 BetweenRounds(): marking 22 ระหว่างรอบเป็น Offline</t>
-  </si>
-  <si>
-    <t>OrderListUserControl.cs:810
-JobProcessService.cs:32
-JobProcessService.cs:46</t>
   </si>
   <si>
     <t>ค่าที่ไม่ใช่ Online/Offline อยู่ใน List
@@ -307,11 +243,6 @@
 Resolve(): แปลง Marking เป็นแผนเครื่อง</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1066
-OrderListUserControl.cs:1304
-MarkingMethodService.cs:43</t>
-  </si>
-  <si>
     <t>10 เริ่มที่ ST3; อื่นเริ่ม ST1
 00 เปลี่ยน Process โดยไม่ส่งเครื่อง
 21/23 ไม่มีแผนที่รองรับ</t>
@@ -325,10 +256,6 @@
 ConfirmStartAsync(): ให้ยืนยันแผนและคิว</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1563
-OrderListUserControl.cs:1441</t>
-  </si>
-  <si>
     <t>ยกเลิกเลือกหรือยืนยัน: ไม่สร้างคิว
 ชื่อที่เลือกติดไปกับคิว</t>
   </si>
@@ -341,11 +268,6 @@
 ConnectionPreflight.CheckAsync(): ต่อหลายปลายทางพร้อมกัน</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:2860
-JobSendService.cs:182
-ConnectionPreflight.cs:6</t>
-  </si>
-  <si>
     <t>ขาดปลายทางที่ต้องใช้: ไม่จองคิว
 ตรวจ TCP ไม่ได้ยืนยันว่าเครื่องพร้อมพิมพ์ทุกเงื่อนไข</t>
   </si>
@@ -358,11 +280,6 @@
 ClaimMachineAsync(): ขอสิทธิ์หัวคิวตาม FIFO</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1614
-OrderListUserControl.cs:1649
-MachineQueueController.js:123</t>
-  </si>
-  <si>
     <t>เครื่องติดงานหรือมีคิวก่อน: รอไว้
 ไม่ล้างคิวเพราะเครื่องไม่ว่าง</t>
   </si>
@@ -375,10 +292,6 @@
 MachineSendBatch.RunAsync(): ส่งเครื่องที่พร้อมพร้อมกัน</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1718
-MachineSendBatch.cs:6</t>
-  </si>
-  <si>
     <t>เครื่องหนึ่งช้า ไม่ล็อกการปล่อยเครื่องอื่น
 เครื่องเดิมในชุดเดียวส่งได้หนึ่งรอบ</t>
   </si>
@@ -389,11 +302,6 @@
     <t>SendQueueStepAsync(): สร้าง token ของรอบส่ง
 BeginQueueSendAsync(): ขอจด QUEUE_DISPATCH
 beginSend(): ล็อกคิว ตรวจสถานะ แล้วตั้ง Process</t>
-  </si>
-  <si>
-    <t>OrderListUserControl.cs:1813
-MachineQueueController.js:342
-queueGuard.js:8</t>
   </si>
   <si>
     <t>คำตอบ begin-send หาย: ไม่ยิงเครื่องเอง
@@ -409,11 +317,6 @@
 SendToOneMkAsync(): SQ → FW → FS/F1 → FM</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1857
-JobSendService.cs:112
-JobSendService.cs:455</t>
-  </si>
-  <si>
     <t>IP ซ้ำ: ส่งทีละหัว
 ช่องข้อความว่างส่งทับงานเก่า
 ค่า Width/Height/Trigger Delay ต้องครบ</t>
@@ -428,11 +331,6 @@
 แล้วอ่านค่ากลับทันที</t>
   </si>
   <si>
-    <t>PlcOrderService.cs:43
-PlcOrderService.cs:81
-OrderListUserControl.cs:2906</t>
-  </si>
-  <si>
     <t>PLC ไม่ผ่านหรือค่ากลับไม่ตรง: เตือน
 โค้ดยังส่ง MK ต่อ ไม่ถือ PLC เป็นด่านหยุด</t>
   </si>
@@ -443,11 +341,6 @@
     <t>SendUvAsync(): ตรวจ CPI และโปรแกรมของคิว
 WriteAsync(): UV1 ลง MK063 / UV2 ลง MK067
 LoadAndStartAsync(): Load KEY85 แล้ว Start KEY83</t>
-  </si>
-  <si>
-    <t>JobSendService.cs:546
-CpiWriteService.cs:10
-UvTcpService.cs:39</t>
   </si>
   <si>
     <t>Load ผ่าน = ส่งข้อมูลแล้ว
@@ -463,10 +356,6 @@
 unknown = ถือคิวไว้ตรวจ</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1813
-MachineQueueController.js:365</t>
-  </si>
-  <si>
     <t>บันทึกผลซ้ำได้ด้วย token เดิม
 ไม่เรียกส่งเครื่องซ้ำเมื่อบันทึกไม่ได้</t>
   </si>
@@ -477,11 +366,6 @@
     <t>PushButtonSettings.Watched(): ST1 รับ MK/UV1/UV2
 PlanBatchRead(): รวมอ่านบิต M เมื่ออยู่ในช่วง
 TickAsync(): จับบิต 0 → 1 แยกเครื่อง</t>
-  </si>
-  <si>
-    <t>PushButtonSettings.cs:69
-PushButtonWatcher.cs:152
-PushButtonWatcher.cs:210</t>
   </si>
   <si>
     <t>ST3 ไม่อ่านปุ่มซ้ำ
@@ -498,11 +382,6 @@
 ProcessMachineQueueAsync(): ส่งเฉพาะเครื่องที่ปล่อย</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:433
-MachineQueueController.js:184
-OrderListUserControl.cs:2181</t>
-  </si>
-  <si>
     <t>กดรัวไม่ข้ามงานถัดไป
 ไม่มีคิวต่อ: MK กลับตำแหน่ง Home
 ปุ่มปล่อยคิวไม่ได้จบ Job</t>
@@ -514,10 +393,6 @@
     <t>HoldForNextRound: เลือกถือ MK ให้รอบสอง
 หรือดันรอบสองไปท้ายคิว
 ResetPositionAsync(): ส่ง Home ไป PostAct ทั้งสองหัว</t>
-  </si>
-  <si>
-    <t>MachineQueueController.js:184
-PlcOrderService.cs:187</t>
   </si>
   <si>
     <t>22 ต้องมีผล MK ครบสองครั้ง
@@ -533,11 +408,6 @@
 RestoreJobAsync(): นำ Job เดิมกลับ Waiting</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:2418
-JobController.js:351
-OrderListUserControl.cs:1152</t>
-  </si>
-  <si>
     <t>sending/unknown: Backend กันเปลี่ยนสถานะ
 10/11/12 จบที่ ST3
 นำกลับไม่ล้างประวัติส่งเก่า</t>
@@ -552,11 +422,6 @@
 NumericInput: จำกัดช่องตัวเลข</t>
   </si>
   <si>
-    <t>OrderDetailUserControl.cs:1587
-OrderDetailUserControl.cs:627
-OrderDetailUserControl.cs:1413</t>
-  </si>
-  <si>
     <t>ปุ่มส่งตรง/ทดสอบอยู่โหมด 99
 ปุ่มทดสอบ PLC ใช้ค่าที่เพิ่งแก้
 ต่างจากทางเริ่มงานจริงที่ PLC ไม่บล็อก MK</t>
@@ -571,11 +436,6 @@
 ToggleAbcAsync(): เปลี่ยนทิศทางข้อความ</t>
   </si>
   <si>
-    <t>OrderDetailUserControl.cs:497
-OrderDetailUserControl.cs:429
-OrderDetailUserControl.cs:836</t>
-  </si>
-  <si>
     <t>ส่งจาก List จะอ่านข้อมูล Backend ใหม่
 SWAP บันทึกไม่ได้ จอกลับค่าเดิม</t>
   </si>
@@ -589,11 +449,6 @@
 IaiUploadAsync(): เก็บระยะใน DB3 และ Backend</t>
   </si>
   <si>
-    <t>OrderDetailUserControl.cs:1920
-OrderDetailUserControl.cs:1979
-ClampService.cs:310</t>
-  </si>
-  <si>
     <t>IAI สั่งจาก Detail ไม่ใช่อัตโนมัติจากปุ่มเริ่ม
 Status อ่านไม่ได้ยังอาจได้ผลคำสั่งสำเร็จ</t>
   </si>
@@ -607,12 +462,6 @@
 PushButtonSettings.Save(): ให้ตัวฟังใช้บิตใหม่ทันที</t>
   </si>
   <si>
-    <t>AppSettingsFile.cs:39
-AppSettingsFile.cs:120
-SettingsStore.cs:47
-PushButtonSettings.cs:108</t>
-  </si>
-  <si>
     <t>เก็บค่าที่ ProgramData/CompactInkjet
 ไฟล์ศูนย์ไบต์กู้จาก .bak เมื่อมี
 เปลี่ยนบิตแล้วไม่นับค่าแรกเป็นการกด</t>
@@ -644,11 +493,6 @@
 SetupEvents(): ซ่อน History</t>
   </si>
   <si>
-    <t>MainShellForm.cs:146
-MarkingMethodService.cs:101
-OrderListUserControl.cs:171</t>
-  </si>
-  <si>
     <t>10 เริ่ม ST3
 11/12 เริ่ม ST1 และจบ ST3</t>
   </si>
@@ -659,10 +503,6 @@
     <t>RefreshDataAsync(): อ่าน Job กับคิวกลาง
 RebindTable(): กรองงาน ST3
 BuildMachineStatus(): ใช้คิวปัจจุบันแยกผลเครื่อง</t>
-  </si>
-  <si>
-    <t>OrderListUserControl.cs:661
-OrderListUserControl.MachineStatus.cs:35</t>
   </si>
   <si>
     <t>คิวรอ / กำลังส่ง / ส่งข้อมูลแล้ว / รอตรวจ
@@ -678,10 +518,6 @@
 ConfirmStartAsync(): ยืนยันก่อนจอง</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1304
-OrderListUserControl.cs:1563</t>
-  </si>
-  <si>
     <t>ST3 ข้ามด่านตรวจเครื่อง/CPI ของ ST1
 ชื่อโปรแกรมติดไปกับคิว UV2</t>
   </si>
@@ -694,10 +530,6 @@
 claim(): เครื่องว่างและเป็นหัวคิวจึงได้ active</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1413
-MachineQueueController.js:123</t>
-  </si>
-  <si>
     <t>ไม่ต้องรอปุ่มปล่อยเมื่อเครื่องว่างและไม่มีคิวก่อน
 ห้ามแซง Job ที่จองมาก่อน</t>
   </si>
@@ -710,11 +542,6 @@
 SendUvAsync(): เขียน CPI และส่งโปรแกรม UV2</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:2181
-OrderListUserControl.cs:1813
-JobSendService.cs:546</t>
-  </si>
-  <si>
     <t>ต้องเปิด Order List ที่ ST1
 ST1 ต้องเข้าถึง IP, CPI และไฟล์ UV2</t>
   </si>
@@ -725,11 +552,6 @@
     <t>LoadAndStartAsync(): ใช้ผล Load ตัดสินการส่งข้อมูล
 SendStepAsync(): เก็บ start_confirmed/start_warning
 finishSend(): บันทึกผลคิวและประวัติพร้อมกัน</t>
-  </si>
-  <si>
-    <t>UvTcpService.cs:39
-OrderListUserControl.cs:1857
-MachineQueueController.js:365</t>
   </si>
   <si>
     <t>Load ผ่านแต่ Start ไม่ผ่าน: ส่งข้อมูลแล้วพร้อมเตือน
@@ -745,11 +567,6 @@
 release(): กันเลขคิวเก่าหรือคิวไม่รู้ผล</t>
   </si>
   <si>
-    <t>PushButtonSettings.cs:69
-PushButtonWatcher.cs:210
-OrderListUserControl.cs:433</t>
-  </si>
-  <si>
     <t>ไม่ได้อ่าน PLC จาก PC ของ ST3
 ปิด ST1 แล้วปุ่มทั้งสามไม่เดินงาน
 กดค้างไม่ปล่อยคิวซ้ำ</t>
@@ -763,10 +580,6 @@
 แสดง Q หรือ Mark Plate / Mark Shim</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:2519
-JobStageService.cs:30</t>
-  </si>
-  <si>
     <t>อยู่ Order Detail แล้วปุ่มจริงยังทำงาน
 ส่งไม่จบแสดงกำลังส่ง/รอตรวจสอบผล</t>
   </si>
@@ -779,11 +592,6 @@
 IaiUploadAsync(): เขียนค่ากลับ DB3 และ Backend</t>
   </si>
   <si>
-    <t>OrderDetailUserControl.cs:1907
-OrderDetailUserControl.cs:1920
-OrderDetailUserControl.cs:1979</t>
-  </si>
-  <si>
     <t>แยก Plate/Shim และแกน X/Z1/Z2
 บันทึกสองปลายทางอาจผ่านเพียงส่วนเดียว</t>
   </si>
@@ -794,11 +602,6 @@
     <t>ApplyStepButtons(): ต้องเปิด ST3_MANUAL_SEND
 RequestRemoteStart(): ปิด Detail แล้วส่ง event
 RequestRemoteStartFromDetailAsync(): อ่านงานสด</t>
-  </si>
-  <si>
-    <t>OrderDetailUserControl.cs:1054
-OrderDetailUserControl.cs:1046
-OrderListUserControl.cs:2547</t>
   </si>
   <si>
     <t>ใช้ขั้นถัดไปของงาน Process
@@ -814,10 +617,6 @@
 แล้วเข้าคิวและทางส่งที่จด token ก่อนยิง</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:1969
-OrderListUserControl.cs:2268</t>
-  </si>
-  <si>
     <t>ทางสำรองใช้กฎคิวด้วย
 ขั้นที่ส่งสำเร็จไปแล้วไม่ยิงซ้ำ</t>
   </si>
@@ -830,10 +629,6 @@
 ShowRemoteErrorsAsync(): แสดงเหตุจาก ST1</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:2065
-OrderListUserControl.cs:2377</t>
-  </si>
-  <si>
     <t>กำลังส่ง/ไม่รู้ผล: ตรวจคิวและเครื่องก่อนกดซ้ำ
 คำเตือนหมดเวลาไม่ใช่ผลตรวจชิ้นงาน</t>
   </si>
@@ -846,10 +641,6 @@
 updateStatus(): เปลี่ยนสถานะพร้อมล้างคิว</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:2418
-JobController.js:351</t>
-  </si>
-  <si>
     <t>Success/Cancel แล้วออกจาก List
 History และการนำกลับอยู่ที่ ST1</t>
   </si>
@@ -862,10 +653,6 @@
 กรองแท็บย่อยหลังกรองงานของ Station</t>
   </si>
   <si>
-    <t>OrderListUserControl.cs:810
-JobProcessService.cs:32</t>
-  </si>
-  <si>
     <t>เป็นตัวกรองรายการ ไม่ใช่ตัวตัดสินเครื่อง Online
 ค่าอื่นดูได้ใน List</t>
   </si>
@@ -880,6 +667,219 @@
   </si>
   <si>
     <t>IAI Upload ลง DB3 กับ Backend แยกกัน ต้องตรวจทั้งสองที่เมื่อแจ้งสำเร็จเพียงบางส่วน</t>
+  </si>
+  <si>
+    <t>Flow: fix-after-it-test @ 896b34b | เลขบรรทัด: write-code | 29/09/2569</t>
+  </si>
+  <si>
+    <t>Program.cs:10
+MainShellForm.cs:92
+AppSettingsFile.cs:13</t>
+  </si>
+  <si>
+    <t>ScanBarcodeUserControl.cs:61
+ScanBarcodeUserControl.cs:83</t>
+  </si>
+  <si>
+    <t>ScanBarcodeUserControl.cs:73
+ScanBarcodeUserControl.cs:71</t>
+  </si>
+  <si>
+    <t>SqliteDataService.cs:112
+SqliteDataService.cs:204</t>
+  </si>
+  <si>
+    <t>ScanBarcodeUserControl.cs:122
+ScanBarcodeUserControl.cs:153
+ScanBarcodeUserControl.cs:136</t>
+  </si>
+  <si>
+    <t>ScanBarcodeUserControl.cs:180
+ScanBarcodeUserControl.cs:271</t>
+  </si>
+  <si>
+    <t>SqliteDataService.cs:26
+SqliteDataService.cs:150</t>
+  </si>
+  <si>
+    <t>ScanBarcodeUserControl.cs:180
+ApiClient.cs:47
+ApiClient.cs:64</t>
+  </si>
+  <si>
+    <t>ApiClient.cs:122
+ApiClient.cs:189</t>
+  </si>
+  <si>
+    <t>ScanBarcodeUserControl.cs:288
+ClampService.cs:154</t>
+  </si>
+  <si>
+    <t>ScanBarcodeUserControl.cs:336
+ScanBarcodeUserControl.cs:343</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:396
+OrderListUserControl.cs:573
+JobProcessService.cs:10</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:122
+OrderListUserControl.cs:396</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:513
+JobProcessService.cs:10
+JobProcessService.cs:15</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:696
+OrderListUserControl.cs:862
+MarkingMethodService.cs:22</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1048
+OrderListUserControl.cs:953</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:2042
+JobSendService.cs:86
+ConnectionPreflight.cs:5</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1089
+OrderListUserControl.cs:1110
+MachineQueueController.js:87</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1177
+MachineSendBatch.cs:5</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1261
+MachineQueueController.js:257
+queueGuard.js:6</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1304
+JobSendService.cs:53
+JobSendService.cs:289</t>
+  </si>
+  <si>
+    <t>PlcOrderService.cs:11
+PlcOrderService.cs:34
+OrderListUserControl.cs:2072</t>
+  </si>
+  <si>
+    <t>JobSendService.cs:336
+CpiWriteService.cs:10
+UvTcpService.cs:27</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1261
+MachineQueueController.js:279</t>
+  </si>
+  <si>
+    <t>PushButtonSettings.cs:33
+PushButtonWatcher.cs:73
+PushButtonWatcher.cs:130</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:233
+MachineQueueController.js:136
+OrderListUserControl.cs:1525</t>
+  </si>
+  <si>
+    <t>MachineQueueController.js:136
+PlcOrderService.cs:100</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1722
+JobController.js:312
+OrderListUserControl.cs:758</t>
+  </si>
+  <si>
+    <t>OrderDetailUserControl.cs:1214
+OrderDetailUserControl.cs:466
+OrderDetailUserControl.cs:1069</t>
+  </si>
+  <si>
+    <t>OrderDetailUserControl.cs:360
+OrderDetailUserControl.cs:323
+OrderDetailUserControl.cs:632</t>
+  </si>
+  <si>
+    <t>OrderDetailUserControl.cs:1489
+OrderDetailUserControl.cs:1545
+ClampService.cs:254</t>
+  </si>
+  <si>
+    <t>AppSettingsFile.cs:13
+AppSettingsFile.cs:62
+SettingsStore.cs:21
+PushButtonSettings.cs:66</t>
+  </si>
+  <si>
+    <t>MainShellForm.cs:92
+MarkingMethodService.cs:57
+OrderListUserControl.cs:96</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:396
+OrderListUserControl.MachineStatus.cs:34</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:862
+OrderListUserControl.cs:1048</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:938
+MachineQueueController.js:87</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1525
+OrderListUserControl.cs:1261
+JobSendService.cs:336</t>
+  </si>
+  <si>
+    <t>UvTcpService.cs:27
+OrderListUserControl.cs:1304
+MachineQueueController.js:279</t>
+  </si>
+  <si>
+    <t>PushButtonSettings.cs:33
+PushButtonWatcher.cs:130
+OrderListUserControl.cs:233</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1794
+JobStageService.cs:10</t>
+  </si>
+  <si>
+    <t>OrderDetailUserControl.cs:1476
+OrderDetailUserControl.cs:1489
+OrderDetailUserControl.cs:1545</t>
+  </si>
+  <si>
+    <t>OrderDetailUserControl.cs:791
+OrderDetailUserControl.cs:783
+OrderListUserControl.cs:1812</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1377
+OrderListUserControl.cs:1606</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1445
+OrderListUserControl.cs:1683</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:1722
+JobController.js:312</t>
+  </si>
+  <si>
+    <t>OrderListUserControl.cs:513
+JobProcessService.cs:10</t>
   </si>
 </sst>
 </file>
@@ -1224,7 +1224,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1232,7 +1232,7 @@
     </row>
     <row r="4" spans="1:4" ht="42" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1246,184 +1246,184 @@
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="82" customHeight="1">
       <c r="A7" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>8</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="82" customHeight="1">
       <c r="A8" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>162</v>
+      </c>
+      <c r="D8" s="5" t="s">
         <v>11</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="82" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>17</v>
+        <v>163</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>18</v>
+        <v>14</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="82" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>21</v>
+        <v>164</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="82" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>25</v>
+        <v>165</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="90" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>29</v>
+        <v>166</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="82" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>32</v>
+        <v>25</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>33</v>
+        <v>167</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="82" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>37</v>
+        <v>168</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>38</v>
+        <v>29</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="82" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>39</v>
+        <v>30</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>41</v>
+        <v>169</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>42</v>
+        <v>32</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="82" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>45</v>
+        <v>170</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="82" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>49</v>
+        <v>171</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>50</v>
+        <v>38</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="82" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>51</v>
+        <v>39</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>52</v>
+        <v>40</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>53</v>
+        <v>172</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>54</v>
+        <v>41</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="20" customHeight="1">
@@ -1434,7 +1434,7 @@
     </row>
     <row r="20" spans="1:4" ht="28" customHeight="1">
       <c r="A20" s="9" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1442,7 +1442,7 @@
     </row>
     <row r="21" spans="1:4" ht="40" customHeight="1">
       <c r="A21" s="7" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
@@ -1450,7 +1450,7 @@
     </row>
     <row r="22" spans="1:4" ht="40" customHeight="1">
       <c r="A22" s="7" t="s">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
@@ -1458,7 +1458,7 @@
     </row>
     <row r="23" spans="1:4" ht="30" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -1511,7 +1511,7 @@
     </row>
     <row r="2" spans="1:4" ht="32" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>59</v>
+        <v>46</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -1519,7 +1519,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1527,7 +1527,7 @@
     </row>
     <row r="4" spans="1:4" ht="42" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>60</v>
+        <v>47</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1541,296 +1541,296 @@
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="82" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>61</v>
+        <v>48</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
+        <v>49</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>63</v>
+        <v>173</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="82" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>67</v>
+        <v>174</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>68</v>
+        <v>53</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>69</v>
+        <v>54</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>71</v>
+        <v>175</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>72</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="82" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>73</v>
+        <v>57</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>75</v>
+        <v>176</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>76</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="90" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>77</v>
+        <v>60</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>78</v>
+        <v>61</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>79</v>
+        <v>177</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>80</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="82" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>81</v>
+        <v>63</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>82</v>
+        <v>64</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>83</v>
+        <v>178</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>84</v>
+        <v>65</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="90" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>85</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>87</v>
+        <v>179</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>88</v>
+        <v>68</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="82" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>89</v>
+        <v>69</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>91</v>
+        <v>180</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>92</v>
+        <v>71</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="90" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>93</v>
+        <v>72</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>95</v>
+        <v>181</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>96</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="90" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>97</v>
+        <v>75</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>98</v>
+        <v>76</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>99</v>
+        <v>182</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>100</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="82" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>103</v>
+        <v>183</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>104</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="90" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>105</v>
+        <v>81</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>106</v>
+        <v>82</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>107</v>
+        <v>184</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="90" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>110</v>
+        <v>85</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>111</v>
+        <v>185</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="90" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>113</v>
+        <v>87</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>114</v>
+        <v>88</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>115</v>
+        <v>186</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>116</v>
+        <v>89</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="82" customHeight="1">
       <c r="A21" s="4" t="s">
-        <v>117</v>
+        <v>90</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>118</v>
+        <v>91</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>119</v>
+        <v>187</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="90" customHeight="1">
       <c r="A22" s="6" t="s">
-        <v>121</v>
+        <v>93</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>122</v>
+        <v>94</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>124</v>
+        <v>95</v>
       </c>
     </row>
     <row r="23" spans="1:4" ht="90" customHeight="1">
       <c r="A23" s="4" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>127</v>
+        <v>189</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>128</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="1:4" ht="90" customHeight="1">
       <c r="A24" s="6" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="B24" s="5" t="s">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>131</v>
+        <v>190</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
     </row>
     <row r="25" spans="1:4" ht="90" customHeight="1">
       <c r="A25" s="4" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>135</v>
+        <v>191</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>136</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:4" ht="109" customHeight="1">
       <c r="A26" s="6" t="s">
-        <v>137</v>
+        <v>105</v>
       </c>
       <c r="B26" s="5" t="s">
-        <v>138</v>
+        <v>106</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>139</v>
+        <v>192</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>140</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:4" ht="20" customHeight="1">
@@ -1841,7 +1841,7 @@
     </row>
     <row r="28" spans="1:4" ht="28" customHeight="1">
       <c r="A28" s="9" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -1849,7 +1849,7 @@
     </row>
     <row r="29" spans="1:4" ht="40" customHeight="1">
       <c r="A29" s="7" t="s">
-        <v>141</v>
+        <v>108</v>
       </c>
       <c r="B29" s="7"/>
       <c r="C29" s="7"/>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="30" spans="1:4" ht="40" customHeight="1">
       <c r="A30" s="7" t="s">
-        <v>142</v>
+        <v>109</v>
       </c>
       <c r="B30" s="7"/>
       <c r="C30" s="7"/>
@@ -1865,7 +1865,7 @@
     </row>
     <row r="31" spans="1:4" ht="40" customHeight="1">
       <c r="A31" s="7" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="B31" s="7"/>
       <c r="C31" s="7"/>
@@ -1873,7 +1873,7 @@
     </row>
     <row r="32" spans="1:4" ht="40" customHeight="1">
       <c r="A32" s="7" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="B32" s="7"/>
       <c r="C32" s="7"/>
@@ -1881,7 +1881,7 @@
     </row>
     <row r="33" spans="1:4" ht="30" customHeight="1">
       <c r="A33" s="7" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B33" s="7"/>
       <c r="C33" s="7"/>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="2" spans="1:4" ht="32" customHeight="1">
       <c r="A2" s="8" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="B2" s="8"/>
       <c r="C2" s="8"/>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
       <c r="A3" s="7" t="s">
-        <v>1</v>
+        <v>160</v>
       </c>
       <c r="B3" s="7"/>
       <c r="C3" s="7"/>
@@ -1952,7 +1952,7 @@
     </row>
     <row r="4" spans="1:4" ht="42" customHeight="1">
       <c r="A4" s="7" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
@@ -1966,212 +1966,212 @@
     </row>
     <row r="6" spans="1:4" ht="30" customHeight="1">
       <c r="A6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="C6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>5</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="82" customHeight="1">
       <c r="A7" s="4" t="s">
-        <v>147</v>
+        <v>114</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>148</v>
+        <v>115</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>149</v>
+        <v>193</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>150</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="90" customHeight="1">
       <c r="A8" s="6" t="s">
-        <v>151</v>
+        <v>117</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>152</v>
+        <v>118</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>153</v>
+        <v>194</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>154</v>
+        <v>119</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="90" customHeight="1">
       <c r="A9" s="4" t="s">
-        <v>155</v>
+        <v>120</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>156</v>
+        <v>121</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>157</v>
+        <v>195</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>158</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="82" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>159</v>
+        <v>123</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>160</v>
+        <v>124</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>161</v>
+        <v>196</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>162</v>
+        <v>125</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="82" customHeight="1">
       <c r="A11" s="4" t="s">
-        <v>163</v>
+        <v>126</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>164</v>
+        <v>127</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>166</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="90" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>167</v>
+        <v>129</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>168</v>
+        <v>130</v>
       </c>
       <c r="C12" s="5" t="s">
-        <v>169</v>
+        <v>198</v>
       </c>
       <c r="D12" s="5" t="s">
-        <v>170</v>
+        <v>131</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="90" customHeight="1">
       <c r="A13" s="4" t="s">
-        <v>171</v>
+        <v>132</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>172</v>
+        <v>133</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="82" customHeight="1">
       <c r="A14" s="6" t="s">
-        <v>175</v>
+        <v>135</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>176</v>
+        <v>136</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>177</v>
+        <v>200</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>178</v>
+        <v>137</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="82" customHeight="1">
       <c r="A15" s="4" t="s">
-        <v>179</v>
+        <v>138</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>180</v>
+        <v>139</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>181</v>
+        <v>201</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>182</v>
+        <v>140</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="82" customHeight="1">
       <c r="A16" s="6" t="s">
-        <v>183</v>
+        <v>141</v>
       </c>
       <c r="B16" s="5" t="s">
-        <v>184</v>
+        <v>142</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>186</v>
+        <v>143</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="90" customHeight="1">
       <c r="A17" s="4" t="s">
-        <v>187</v>
+        <v>144</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>188</v>
+        <v>145</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>190</v>
+        <v>146</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="82" customHeight="1">
       <c r="A18" s="6" t="s">
-        <v>191</v>
+        <v>147</v>
       </c>
       <c r="B18" s="5" t="s">
-        <v>192</v>
+        <v>148</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>193</v>
+        <v>204</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>194</v>
+        <v>149</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="82" customHeight="1">
       <c r="A19" s="4" t="s">
-        <v>195</v>
+        <v>150</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>196</v>
+        <v>151</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>198</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="82" customHeight="1">
       <c r="A20" s="6" t="s">
-        <v>199</v>
+        <v>153</v>
       </c>
       <c r="B20" s="5" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>202</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" spans="1:4" ht="20" customHeight="1">
@@ -2182,7 +2182,7 @@
     </row>
     <row r="22" spans="1:4" ht="28" customHeight="1">
       <c r="A22" s="9" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -2190,7 +2190,7 @@
     </row>
     <row r="23" spans="1:4" ht="40" customHeight="1">
       <c r="A23" s="7" t="s">
-        <v>203</v>
+        <v>156</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
@@ -2198,7 +2198,7 @@
     </row>
     <row r="24" spans="1:4" ht="40" customHeight="1">
       <c r="A24" s="7" t="s">
-        <v>204</v>
+        <v>157</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
@@ -2206,7 +2206,7 @@
     </row>
     <row r="25" spans="1:4" ht="40" customHeight="1">
       <c r="A25" s="7" t="s">
-        <v>205</v>
+        <v>158</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
@@ -2214,7 +2214,7 @@
     </row>
     <row r="26" spans="1:4" ht="40" customHeight="1">
       <c r="A26" s="7" t="s">
-        <v>206</v>
+        <v>159</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -2222,7 +2222,7 @@
     </row>
     <row r="27" spans="1:4" ht="30" customHeight="1">
       <c r="A27" s="7" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="B27" s="7"/>
       <c r="C27" s="7"/>
